--- a/data/data_dictionnary.xlsx
+++ b/data/data_dictionnary.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lapin\Documents\Nerd stuff\Spells\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA243882-AA75-43DF-9EE0-0EACD974FBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA095A07-861D-48F7-918C-A27B6D8F6ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Description" sheetId="1" r:id="rId1"/>
+    <sheet name="dmg_type" sheetId="3" r:id="rId2"/>
+    <sheet name="schools" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,17 +27,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
   <si>
     <t>name</t>
   </si>
   <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>values</t>
-  </si>
-  <si>
     <t>source</t>
   </si>
   <si>
@@ -94,14 +90,118 @@
   </si>
   <si>
     <t>Source material</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>Abjuration</t>
+  </si>
+  <si>
+    <t>Conjuration</t>
+  </si>
+  <si>
+    <t>Divination</t>
+  </si>
+  <si>
+    <t>Enhantement</t>
+  </si>
+  <si>
+    <t>Evocation</t>
+  </si>
+  <si>
+    <t>Illusion</t>
+  </si>
+  <si>
+    <t>Necromancy</t>
+  </si>
+  <si>
+    <t>Transmutation</t>
+  </si>
+  <si>
+    <t>sub_schools</t>
+  </si>
+  <si>
+    <t>Attribut</t>
+  </si>
+  <si>
+    <t>Ddescription</t>
+  </si>
+  <si>
+    <t>Values</t>
+  </si>
+  <si>
+    <t>dmg_type</t>
+  </si>
+  <si>
+    <t>Damage type</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>Bludgeoning</t>
+  </si>
+  <si>
+    <t>Radiant</t>
+  </si>
+  <si>
+    <t>Necrotic</t>
+  </si>
+  <si>
+    <t>Psychic</t>
+  </si>
+  <si>
+    <t>Cold</t>
+  </si>
+  <si>
+    <t>Force</t>
+  </si>
+  <si>
+    <t>Elemental</t>
+  </si>
+  <si>
+    <t>Lightning</t>
+  </si>
+  <si>
+    <t>Piercing</t>
+  </si>
+  <si>
+    <t>Thunder</t>
+  </si>
+  <si>
+    <t>Acid</t>
+  </si>
+  <si>
+    <t>Poison</t>
+  </si>
+  <si>
+    <t>Slashing</t>
+  </si>
+  <si>
+    <t>Physical</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -129,13 +229,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -146,6 +253,40 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{43153FAB-9E0C-4D8D-A042-39DF964C1FA1}" name="Table3" displayName="Table3" ref="A1:C22" totalsRowShown="0">
+  <autoFilter ref="A1:C22" xr:uid="{43153FAB-9E0C-4D8D-A042-39DF964C1FA1}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{7F1BAB86-BCC3-43FD-B64F-AB2C9C305D09}" name="Attribut" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{7EF40B69-B9C9-4E37-AEEC-631969FB9AED}" name="Ddescription"/>
+    <tableColumn id="3" xr3:uid="{A4CF6E10-343B-493A-8834-0A0EBEB8D932}" name="Values"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5FB9CDB-3E26-495E-964F-B9E7A491F944}" name="Table2" displayName="Table2" ref="A1:B16" totalsRowShown="0">
+  <autoFilter ref="A1:B16" xr:uid="{A5FB9CDB-3E26-495E-964F-B9E7A491F944}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{DE7FFAF3-E29A-4300-8702-B0E49B0FC4FB}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{110C3A31-7098-4522-A2B0-9D03D1D36D27}" name="value"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAC60752-87AA-4DC1-83BC-6E85F33BFB2C}" name="Table1" displayName="Table1" ref="A1:B9" totalsRowShown="0">
+  <autoFilter ref="A1:B9" xr:uid="{DAC60752-87AA-4DC1-83BC-6E85F33BFB2C}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{2DD0C663-6A0F-45B2-A76E-6B1A53B04333}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{4CE3F516-C3C3-4B74-B972-24E470B78613}" name="value"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -411,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -420,117 +561,371 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{001CD0DF-2086-4D9D-A6FB-D83B86C8185C}">
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E61A61D9-FE13-4E2A-BBF6-037B993FAA4F}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>